--- a/Unity/Assets/Config/Excel/PetEggDuiHuanConfig.xlsx
+++ b/Unity/Assets/Config/Excel/PetEggDuiHuanConfig.xlsx
@@ -1,27 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25427"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WeiJingGame_Hot\trunk_weijing\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63658512-C701-4ED7-AFFD-FF81F7A99C3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1755" yWindow="1410" windowWidth="27045" windowHeight="14790" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="21495" windowHeight="12045"/>
   </bookViews>
   <sheets>
     <sheet name="PetEggDuiHuanProto" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -29,106 +27,140 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
   <si>
-    <t>string</t>
+    <t>##var</t>
   </si>
   <si>
-    <t>int</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>CostItems</t>
+  </si>
+  <si>
+    <t>DropID</t>
+  </si>
+  <si>
+    <t>##type</t>
   </si>
   <si>
     <t>int</t>
   </si>
   <si>
-    <t>Id</t>
+    <t>string</t>
   </si>
   <si>
-    <t>Id</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <t>##</t>
+  </si>
+  <si>
+    <t>消耗</t>
   </si>
   <si>
     <t>掉落ID</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>DropID</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>消耗</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>CostItems</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>10000132;10</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>10000132;25</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>10000132;50</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
   <fonts count="26">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Helvetica Neue"/>
-      <family val="2"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Helvetica Neue"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="Helvetica Neue"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="Helvetica Neue"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -137,7 +169,6 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="Helvetica Neue"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -146,31 +177,6 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="Helvetica Neue"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Helvetica Neue"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Helvetica Neue"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Helvetica Neue"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -178,7 +184,6 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="Helvetica Neue"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -187,7 +192,6 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="Helvetica Neue"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -196,15 +200,6 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Helvetica Neue"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Helvetica Neue"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -213,24 +208,13 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="Helvetica Neue"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="Helvetica Neue"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Helvetica Neue"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -239,7 +223,27 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Helvetica Neue"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Helvetica Neue"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -247,7 +251,6 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="Helvetica Neue"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -255,40 +258,17 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Helvetica Neue"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Tahoma"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Helvetica Neue"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -297,192 +277,211 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor indexed="10"/>
-        <bgColor auto="1"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="12"/>
-        <bgColor auto="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -505,8 +504,8 @@
       <top style="thin">
         <color indexed="9"/>
       </top>
-      <bottom style="thin">
-        <color indexed="9"/>
+      <bottom style="hair">
+        <color indexed="11"/>
       </bottom>
       <diagonal/>
     </border>
@@ -520,8 +519,8 @@
       <top style="thin">
         <color indexed="9"/>
       </top>
-      <bottom style="hair">
-        <color indexed="11"/>
+      <bottom style="thin">
+        <color indexed="9"/>
       </bottom>
       <diagonal/>
     </border>
@@ -536,6 +535,21 @@
         <color indexed="11"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -561,7 +575,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color theme="4" tint="0.399975585192419"/>
       </bottom>
       <diagonal/>
     </border>
@@ -596,15 +610,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -620,17 +625,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -646,426 +645,458 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="98">
+  <cellStyleXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="98">
-    <cellStyle name="20% - 强调文字颜色 1 2" xfId="50" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 2 2" xfId="82" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 3" xfId="66" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 2" xfId="52" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 2 2" xfId="84" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 3" xfId="68" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 2" xfId="54" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 2 2" xfId="86" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 3" xfId="70" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 2" xfId="56" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 2 2" xfId="88" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 3" xfId="72" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 2" xfId="58" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 2 2" xfId="90" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 3" xfId="74" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 2" xfId="60" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 2 2" xfId="92" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 3" xfId="76" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
-    <cellStyle name="20% - 着色 1" xfId="18" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 2" xfId="22" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 3" xfId="26" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 4" xfId="30" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 5" xfId="34" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 6" xfId="38" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - 强调文字颜色 1 2" xfId="51" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 2 2" xfId="83" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 3" xfId="67" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 2" xfId="53" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 2 2" xfId="85" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 3" xfId="69" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 2" xfId="55" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 2 2" xfId="87" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 3" xfId="71" xr:uid="{00000000-0005-0000-0000-000023000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 2" xfId="57" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 2 2" xfId="89" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 3" xfId="73" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 2" xfId="59" xr:uid="{00000000-0005-0000-0000-000029000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 2 2" xfId="91" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 3" xfId="75" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 2" xfId="61" xr:uid="{00000000-0005-0000-0000-00002D000000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 2 2" xfId="93" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 3" xfId="77" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
-    <cellStyle name="40% - 着色 1" xfId="19" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 2" xfId="23" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 3" xfId="27" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 4" xfId="31" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 5" xfId="35" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 6" xfId="39" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 1" xfId="20" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 2" xfId="24" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 3" xfId="28" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 4" xfId="32" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 5" xfId="36" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 6" xfId="40" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="标题" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="标题 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="标题 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="标题 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="标题 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="差" xfId="7" builtinId="27" customBuiltin="1"/>
+  <cellStyles count="106">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="43" xr:uid="{00000000-0005-0000-0000-00003D000000}"/>
-    <cellStyle name="常规 2 2" xfId="45" xr:uid="{00000000-0005-0000-0000-00003E000000}"/>
-    <cellStyle name="常规 2 3" xfId="44" xr:uid="{00000000-0005-0000-0000-00003F000000}"/>
-    <cellStyle name="常规 2 3 2" xfId="49" xr:uid="{00000000-0005-0000-0000-000040000000}"/>
-    <cellStyle name="常规 2 3 2 2" xfId="65" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
-    <cellStyle name="常规 2 3 2 2 2" xfId="97" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
-    <cellStyle name="常规 2 3 2 3" xfId="81" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
-    <cellStyle name="常规 2 3 3" xfId="62" xr:uid="{00000000-0005-0000-0000-000044000000}"/>
-    <cellStyle name="常规 2 3 3 2" xfId="94" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
-    <cellStyle name="常规 2 3 4" xfId="78" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
-    <cellStyle name="常规 3" xfId="42" xr:uid="{00000000-0005-0000-0000-000047000000}"/>
-    <cellStyle name="常规 4" xfId="48" xr:uid="{00000000-0005-0000-0000-000048000000}"/>
-    <cellStyle name="常规 5" xfId="46" xr:uid="{00000000-0005-0000-0000-000049000000}"/>
-    <cellStyle name="常规 5 2" xfId="63" xr:uid="{00000000-0005-0000-0000-00004A000000}"/>
-    <cellStyle name="常规 5 2 2" xfId="95" xr:uid="{00000000-0005-0000-0000-00004B000000}"/>
-    <cellStyle name="常规 5 3" xfId="79" xr:uid="{00000000-0005-0000-0000-00004C000000}"/>
-    <cellStyle name="常规 6" xfId="41" xr:uid="{00000000-0005-0000-0000-00004D000000}"/>
-    <cellStyle name="好" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="汇总" xfId="16" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="计算" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="检查单元格" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="解释性文本" xfId="15" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="警告文本" xfId="14" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="链接单元格" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="适中" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="输出" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="输入" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="着色 1" xfId="17" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="着色 2" xfId="21" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="着色 3" xfId="25" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="着色 4" xfId="29" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="着色 5" xfId="33" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="着色 6" xfId="37" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="注释 2" xfId="47" xr:uid="{00000000-0005-0000-0000-00005E000000}"/>
-    <cellStyle name="注释 2 2" xfId="64" xr:uid="{00000000-0005-0000-0000-00005F000000}"/>
-    <cellStyle name="注释 2 2 2" xfId="96" xr:uid="{00000000-0005-0000-0000-000060000000}"/>
-    <cellStyle name="注释 2 3" xfId="80" xr:uid="{00000000-0005-0000-0000-000061000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="20% - 强调文字颜色 1 2" xfId="49"/>
+    <cellStyle name="20% - 强调文字颜色 1 2 2" xfId="50"/>
+    <cellStyle name="20% - 强调文字颜色 1 3" xfId="51"/>
+    <cellStyle name="20% - 强调文字颜色 2 2" xfId="52"/>
+    <cellStyle name="20% - 强调文字颜色 2 2 2" xfId="53"/>
+    <cellStyle name="20% - 强调文字颜色 2 3" xfId="54"/>
+    <cellStyle name="20% - 强调文字颜色 3 2" xfId="55"/>
+    <cellStyle name="20% - 强调文字颜色 3 2 2" xfId="56"/>
+    <cellStyle name="20% - 强调文字颜色 3 3" xfId="57"/>
+    <cellStyle name="20% - 强调文字颜色 4 2" xfId="58"/>
+    <cellStyle name="20% - 强调文字颜色 4 2 2" xfId="59"/>
+    <cellStyle name="20% - 强调文字颜色 4 3" xfId="60"/>
+    <cellStyle name="20% - 强调文字颜色 5 2" xfId="61"/>
+    <cellStyle name="20% - 强调文字颜色 5 2 2" xfId="62"/>
+    <cellStyle name="20% - 强调文字颜色 5 3" xfId="63"/>
+    <cellStyle name="20% - 强调文字颜色 6 2" xfId="64"/>
+    <cellStyle name="20% - 强调文字颜色 6 2 2" xfId="65"/>
+    <cellStyle name="20% - 强调文字颜色 6 3" xfId="66"/>
+    <cellStyle name="40% - 强调文字颜色 1 2" xfId="67"/>
+    <cellStyle name="40% - 强调文字颜色 1 2 2" xfId="68"/>
+    <cellStyle name="40% - 强调文字颜色 1 3" xfId="69"/>
+    <cellStyle name="40% - 强调文字颜色 2 2" xfId="70"/>
+    <cellStyle name="40% - 强调文字颜色 2 2 2" xfId="71"/>
+    <cellStyle name="40% - 强调文字颜色 2 3" xfId="72"/>
+    <cellStyle name="40% - 强调文字颜色 3 2" xfId="73"/>
+    <cellStyle name="40% - 强调文字颜色 3 2 2" xfId="74"/>
+    <cellStyle name="40% - 强调文字颜色 3 3" xfId="75"/>
+    <cellStyle name="40% - 强调文字颜色 4 2" xfId="76"/>
+    <cellStyle name="40% - 强调文字颜色 4 2 2" xfId="77"/>
+    <cellStyle name="40% - 强调文字颜色 4 3" xfId="78"/>
+    <cellStyle name="40% - 强调文字颜色 5 2" xfId="79"/>
+    <cellStyle name="40% - 强调文字颜色 5 2 2" xfId="80"/>
+    <cellStyle name="40% - 强调文字颜色 5 3" xfId="81"/>
+    <cellStyle name="40% - 强调文字颜色 6 2" xfId="82"/>
+    <cellStyle name="40% - 强调文字颜色 6 2 2" xfId="83"/>
+    <cellStyle name="40% - 强调文字颜色 6 3" xfId="84"/>
+    <cellStyle name="常规 2" xfId="85"/>
+    <cellStyle name="常规 2 2" xfId="86"/>
+    <cellStyle name="常规 2 3" xfId="87"/>
+    <cellStyle name="常规 2 3 2" xfId="88"/>
+    <cellStyle name="常规 2 3 2 2" xfId="89"/>
+    <cellStyle name="常规 2 3 2 2 2" xfId="90"/>
+    <cellStyle name="常规 2 3 2 3" xfId="91"/>
+    <cellStyle name="常规 2 3 3" xfId="92"/>
+    <cellStyle name="常规 2 3 3 2" xfId="93"/>
+    <cellStyle name="常规 2 3 4" xfId="94"/>
+    <cellStyle name="常规 3" xfId="95"/>
+    <cellStyle name="常规 4" xfId="96"/>
+    <cellStyle name="常规 5" xfId="97"/>
+    <cellStyle name="常规 5 2" xfId="98"/>
+    <cellStyle name="常规 5 2 2" xfId="99"/>
+    <cellStyle name="常规 5 3" xfId="100"/>
+    <cellStyle name="常规 6" xfId="101"/>
+    <cellStyle name="注释 2" xfId="102"/>
+    <cellStyle name="注释 2 2" xfId="103"/>
+    <cellStyle name="注释 2 2 2" xfId="104"/>
+    <cellStyle name="注释 2 3" xfId="105"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FF3F3F3F"/>
-      <rgbColor rgb="FF7F7F7F"/>
-      <rgbColor rgb="FFD8D8D8"/>
-      <rgbColor rgb="FFAAAAAA"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="003F3F3F"/>
+      <rgbColor rgb="007F7F7F"/>
+      <rgbColor rgb="00D8D8D8"/>
+      <rgbColor rgb="00AAAAAA"/>
       <rgbColor rgb="00FF00FF"/>
       <rgbColor rgb="0000FFFF"/>
       <rgbColor rgb="00800000"/>
@@ -1121,9 +1152,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1354,7 +1382,6 @@
             </a:srgbClr>
           </a:outerShdw>
         </a:effectLst>
-        <a:sp3d/>
       </a:spPr>
       <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr">
         <a:spAutoFit/>
@@ -1374,7 +1401,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1384,10 +1410,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Calibri"/>
-            <a:ea typeface="Calibri"/>
-            <a:cs typeface="Calibri"/>
-            <a:sym typeface="Calibri"/>
+            <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+            <a:ea typeface="Calibri" panose="020F0502020204030204"/>
+            <a:cs typeface="Calibri" panose="020F0502020204030204"/>
+            <a:sym typeface="Calibri" panose="020F0502020204030204"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -1404,7 +1430,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1430,7 +1455,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1456,7 +1480,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1482,7 +1505,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1508,7 +1530,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1534,7 +1555,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1560,7 +1580,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1586,7 +1605,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1612,7 +1630,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1655,7 +1672,6 @@
             </a:srgbClr>
           </a:outerShdw>
         </a:effectLst>
-        <a:sp3d/>
       </a:spPr>
       <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:noAutofit/>
@@ -1675,7 +1691,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1701,7 +1716,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1727,7 +1741,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1753,7 +1766,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1779,7 +1791,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1805,7 +1816,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1831,7 +1841,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1857,7 +1866,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1883,7 +1891,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1909,7 +1916,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1942,8 +1948,6 @@
           <a:noFill/>
           <a:miter lim="400000"/>
         </a:ln>
-        <a:effectLst/>
-        <a:sp3d/>
       </a:spPr>
       <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:spAutoFit/>
@@ -1963,7 +1967,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1973,10 +1976,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Calibri"/>
-            <a:ea typeface="Calibri"/>
-            <a:cs typeface="Calibri"/>
-            <a:sym typeface="Calibri"/>
+            <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+            <a:ea typeface="Calibri" panose="020F0502020204030204"/>
+            <a:cs typeface="Calibri" panose="020F0502020204030204"/>
+            <a:sym typeface="Calibri" panose="020F0502020204030204"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -1993,7 +1996,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -2019,7 +2021,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -2045,7 +2046,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -2071,7 +2071,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -2097,7 +2096,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -2123,7 +2121,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -2149,7 +2146,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -2175,7 +2171,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -2201,7 +2196,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -2228,97 +2222,497 @@
       </a:style>
     </a:txDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:GV8"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:GU6"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" customHeight="1" outlineLevelRow="5"/>
   <cols>
-    <col min="3" max="3" width="11" style="1" customWidth="1"/>
-    <col min="4" max="4" width="20.375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.875" style="1" customWidth="1"/>
-    <col min="6" max="204" width="8.875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="23.875" style="1" customWidth="1"/>
+    <col min="5" max="203" width="8.875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:5" s="5" customFormat="1" ht="14.25">
-      <c r="C1" s="6"/>
-    </row>
-    <row r="2" spans="3:5" ht="13.5" customHeight="1">
-      <c r="D2" s="5"/>
-    </row>
-    <row r="3" spans="3:5" ht="20.100000000000001" customHeight="1">
-      <c r="C3" s="7" t="s">
+    <row r="1" customFormat="1" ht="20.1" customHeight="1" spans="1:203">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+      <c r="AH1" s="1"/>
+      <c r="AI1" s="1"/>
+      <c r="AJ1" s="1"/>
+      <c r="AK1" s="1"/>
+      <c r="AL1" s="1"/>
+      <c r="AM1" s="1"/>
+      <c r="AN1" s="1"/>
+      <c r="AO1" s="1"/>
+      <c r="AP1" s="1"/>
+      <c r="AQ1" s="1"/>
+      <c r="AR1" s="1"/>
+      <c r="AS1" s="1"/>
+      <c r="AT1" s="1"/>
+      <c r="AU1" s="1"/>
+      <c r="AV1" s="1"/>
+      <c r="AW1" s="1"/>
+      <c r="AX1" s="1"/>
+      <c r="AY1" s="1"/>
+      <c r="AZ1" s="1"/>
+      <c r="BA1" s="1"/>
+      <c r="BB1" s="1"/>
+      <c r="BC1" s="1"/>
+      <c r="BD1" s="1"/>
+      <c r="BE1" s="1"/>
+      <c r="BF1" s="1"/>
+      <c r="BG1" s="1"/>
+      <c r="BH1" s="1"/>
+      <c r="BI1" s="1"/>
+      <c r="BJ1" s="1"/>
+      <c r="BK1" s="1"/>
+      <c r="BL1" s="1"/>
+      <c r="BM1" s="1"/>
+      <c r="BN1" s="1"/>
+      <c r="BO1" s="1"/>
+      <c r="BP1" s="1"/>
+      <c r="BQ1" s="1"/>
+      <c r="BR1" s="1"/>
+      <c r="BS1" s="1"/>
+      <c r="BT1" s="1"/>
+      <c r="BU1" s="1"/>
+      <c r="BV1" s="1"/>
+      <c r="BW1" s="1"/>
+      <c r="BX1" s="1"/>
+      <c r="BY1" s="1"/>
+      <c r="BZ1" s="1"/>
+      <c r="CA1" s="1"/>
+      <c r="CB1" s="1"/>
+      <c r="CC1" s="1"/>
+      <c r="CD1" s="1"/>
+      <c r="CE1" s="1"/>
+      <c r="CF1" s="1"/>
+      <c r="CG1" s="1"/>
+      <c r="CH1" s="1"/>
+      <c r="CI1" s="1"/>
+      <c r="CJ1" s="1"/>
+      <c r="CK1" s="1"/>
+      <c r="CL1" s="1"/>
+      <c r="CM1" s="1"/>
+      <c r="CN1" s="1"/>
+      <c r="CO1" s="1"/>
+      <c r="CP1" s="1"/>
+      <c r="CQ1" s="1"/>
+      <c r="CR1" s="1"/>
+      <c r="CS1" s="1"/>
+      <c r="CT1" s="1"/>
+      <c r="CU1" s="1"/>
+      <c r="CV1" s="1"/>
+      <c r="CW1" s="1"/>
+      <c r="CX1" s="1"/>
+      <c r="CY1" s="1"/>
+      <c r="CZ1" s="1"/>
+      <c r="DA1" s="1"/>
+      <c r="DB1" s="1"/>
+      <c r="DC1" s="1"/>
+      <c r="DD1" s="1"/>
+      <c r="DE1" s="1"/>
+      <c r="DF1" s="1"/>
+      <c r="DG1" s="1"/>
+      <c r="DH1" s="1"/>
+      <c r="DI1" s="1"/>
+      <c r="DJ1" s="1"/>
+      <c r="DK1" s="1"/>
+      <c r="DL1" s="1"/>
+      <c r="DM1" s="1"/>
+      <c r="DN1" s="1"/>
+      <c r="DO1" s="1"/>
+      <c r="DP1" s="1"/>
+      <c r="DQ1" s="1"/>
+      <c r="DR1" s="1"/>
+      <c r="DS1" s="1"/>
+      <c r="DT1" s="1"/>
+      <c r="DU1" s="1"/>
+      <c r="DV1" s="1"/>
+      <c r="DW1" s="1"/>
+      <c r="DX1" s="1"/>
+      <c r="DY1" s="1"/>
+      <c r="DZ1" s="1"/>
+      <c r="EA1" s="1"/>
+      <c r="EB1" s="1"/>
+      <c r="EC1" s="1"/>
+      <c r="ED1" s="1"/>
+      <c r="EE1" s="1"/>
+      <c r="EF1" s="1"/>
+      <c r="EG1" s="1"/>
+      <c r="EH1" s="1"/>
+      <c r="EI1" s="1"/>
+      <c r="EJ1" s="1"/>
+      <c r="EK1" s="1"/>
+      <c r="EL1" s="1"/>
+      <c r="EM1" s="1"/>
+      <c r="EN1" s="1"/>
+      <c r="EO1" s="1"/>
+      <c r="EP1" s="1"/>
+      <c r="EQ1" s="1"/>
+      <c r="ER1" s="1"/>
+      <c r="ES1" s="1"/>
+      <c r="ET1" s="1"/>
+      <c r="EU1" s="1"/>
+      <c r="EV1" s="1"/>
+      <c r="EW1" s="1"/>
+      <c r="EX1" s="1"/>
+      <c r="EY1" s="1"/>
+      <c r="EZ1" s="1"/>
+      <c r="FA1" s="1"/>
+      <c r="FB1" s="1"/>
+      <c r="FC1" s="1"/>
+      <c r="FD1" s="1"/>
+      <c r="FE1" s="1"/>
+      <c r="FF1" s="1"/>
+      <c r="FG1" s="1"/>
+      <c r="FH1" s="1"/>
+      <c r="FI1" s="1"/>
+      <c r="FJ1" s="1"/>
+      <c r="FK1" s="1"/>
+      <c r="FL1" s="1"/>
+      <c r="FM1" s="1"/>
+      <c r="FN1" s="1"/>
+      <c r="FO1" s="1"/>
+      <c r="FP1" s="1"/>
+      <c r="FQ1" s="1"/>
+      <c r="FR1" s="1"/>
+      <c r="FS1" s="1"/>
+      <c r="FT1" s="1"/>
+      <c r="FU1" s="1"/>
+      <c r="FV1" s="1"/>
+      <c r="FW1" s="1"/>
+      <c r="FX1" s="1"/>
+      <c r="FY1" s="1"/>
+      <c r="FZ1" s="1"/>
+      <c r="GA1" s="1"/>
+      <c r="GB1" s="1"/>
+      <c r="GC1" s="1"/>
+      <c r="GD1" s="1"/>
+      <c r="GE1" s="1"/>
+      <c r="GF1" s="1"/>
+      <c r="GG1" s="1"/>
+      <c r="GH1" s="1"/>
+      <c r="GI1" s="1"/>
+      <c r="GJ1" s="1"/>
+      <c r="GK1" s="1"/>
+      <c r="GL1" s="1"/>
+      <c r="GM1" s="1"/>
+      <c r="GN1" s="1"/>
+      <c r="GO1" s="1"/>
+      <c r="GP1" s="1"/>
+      <c r="GQ1" s="1"/>
+      <c r="GR1" s="1"/>
+      <c r="GS1" s="1"/>
+      <c r="GT1" s="1"/>
+      <c r="GU1" s="1"/>
+    </row>
+    <row r="2" customFormat="1" ht="20.1" customHeight="1" spans="1:203">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="1"/>
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="1"/>
+      <c r="AG2" s="1"/>
+      <c r="AH2" s="1"/>
+      <c r="AI2" s="1"/>
+      <c r="AJ2" s="1"/>
+      <c r="AK2" s="1"/>
+      <c r="AL2" s="1"/>
+      <c r="AM2" s="1"/>
+      <c r="AN2" s="1"/>
+      <c r="AO2" s="1"/>
+      <c r="AP2" s="1"/>
+      <c r="AQ2" s="1"/>
+      <c r="AR2" s="1"/>
+      <c r="AS2" s="1"/>
+      <c r="AT2" s="1"/>
+      <c r="AU2" s="1"/>
+      <c r="AV2" s="1"/>
+      <c r="AW2" s="1"/>
+      <c r="AX2" s="1"/>
+      <c r="AY2" s="1"/>
+      <c r="AZ2" s="1"/>
+      <c r="BA2" s="1"/>
+      <c r="BB2" s="1"/>
+      <c r="BC2" s="1"/>
+      <c r="BD2" s="1"/>
+      <c r="BE2" s="1"/>
+      <c r="BF2" s="1"/>
+      <c r="BG2" s="1"/>
+      <c r="BH2" s="1"/>
+      <c r="BI2" s="1"/>
+      <c r="BJ2" s="1"/>
+      <c r="BK2" s="1"/>
+      <c r="BL2" s="1"/>
+      <c r="BM2" s="1"/>
+      <c r="BN2" s="1"/>
+      <c r="BO2" s="1"/>
+      <c r="BP2" s="1"/>
+      <c r="BQ2" s="1"/>
+      <c r="BR2" s="1"/>
+      <c r="BS2" s="1"/>
+      <c r="BT2" s="1"/>
+      <c r="BU2" s="1"/>
+      <c r="BV2" s="1"/>
+      <c r="BW2" s="1"/>
+      <c r="BX2" s="1"/>
+      <c r="BY2" s="1"/>
+      <c r="BZ2" s="1"/>
+      <c r="CA2" s="1"/>
+      <c r="CB2" s="1"/>
+      <c r="CC2" s="1"/>
+      <c r="CD2" s="1"/>
+      <c r="CE2" s="1"/>
+      <c r="CF2" s="1"/>
+      <c r="CG2" s="1"/>
+      <c r="CH2" s="1"/>
+      <c r="CI2" s="1"/>
+      <c r="CJ2" s="1"/>
+      <c r="CK2" s="1"/>
+      <c r="CL2" s="1"/>
+      <c r="CM2" s="1"/>
+      <c r="CN2" s="1"/>
+      <c r="CO2" s="1"/>
+      <c r="CP2" s="1"/>
+      <c r="CQ2" s="1"/>
+      <c r="CR2" s="1"/>
+      <c r="CS2" s="1"/>
+      <c r="CT2" s="1"/>
+      <c r="CU2" s="1"/>
+      <c r="CV2" s="1"/>
+      <c r="CW2" s="1"/>
+      <c r="CX2" s="1"/>
+      <c r="CY2" s="1"/>
+      <c r="CZ2" s="1"/>
+      <c r="DA2" s="1"/>
+      <c r="DB2" s="1"/>
+      <c r="DC2" s="1"/>
+      <c r="DD2" s="1"/>
+      <c r="DE2" s="1"/>
+      <c r="DF2" s="1"/>
+      <c r="DG2" s="1"/>
+      <c r="DH2" s="1"/>
+      <c r="DI2" s="1"/>
+      <c r="DJ2" s="1"/>
+      <c r="DK2" s="1"/>
+      <c r="DL2" s="1"/>
+      <c r="DM2" s="1"/>
+      <c r="DN2" s="1"/>
+      <c r="DO2" s="1"/>
+      <c r="DP2" s="1"/>
+      <c r="DQ2" s="1"/>
+      <c r="DR2" s="1"/>
+      <c r="DS2" s="1"/>
+      <c r="DT2" s="1"/>
+      <c r="DU2" s="1"/>
+      <c r="DV2" s="1"/>
+      <c r="DW2" s="1"/>
+      <c r="DX2" s="1"/>
+      <c r="DY2" s="1"/>
+      <c r="DZ2" s="1"/>
+      <c r="EA2" s="1"/>
+      <c r="EB2" s="1"/>
+      <c r="EC2" s="1"/>
+      <c r="ED2" s="1"/>
+      <c r="EE2" s="1"/>
+      <c r="EF2" s="1"/>
+      <c r="EG2" s="1"/>
+      <c r="EH2" s="1"/>
+      <c r="EI2" s="1"/>
+      <c r="EJ2" s="1"/>
+      <c r="EK2" s="1"/>
+      <c r="EL2" s="1"/>
+      <c r="EM2" s="1"/>
+      <c r="EN2" s="1"/>
+      <c r="EO2" s="1"/>
+      <c r="EP2" s="1"/>
+      <c r="EQ2" s="1"/>
+      <c r="ER2" s="1"/>
+      <c r="ES2" s="1"/>
+      <c r="ET2" s="1"/>
+      <c r="EU2" s="1"/>
+      <c r="EV2" s="1"/>
+      <c r="EW2" s="1"/>
+      <c r="EX2" s="1"/>
+      <c r="EY2" s="1"/>
+      <c r="EZ2" s="1"/>
+      <c r="FA2" s="1"/>
+      <c r="FB2" s="1"/>
+      <c r="FC2" s="1"/>
+      <c r="FD2" s="1"/>
+      <c r="FE2" s="1"/>
+      <c r="FF2" s="1"/>
+      <c r="FG2" s="1"/>
+      <c r="FH2" s="1"/>
+      <c r="FI2" s="1"/>
+      <c r="FJ2" s="1"/>
+      <c r="FK2" s="1"/>
+      <c r="FL2" s="1"/>
+      <c r="FM2" s="1"/>
+      <c r="FN2" s="1"/>
+      <c r="FO2" s="1"/>
+      <c r="FP2" s="1"/>
+      <c r="FQ2" s="1"/>
+      <c r="FR2" s="1"/>
+      <c r="FS2" s="1"/>
+      <c r="FT2" s="1"/>
+      <c r="FU2" s="1"/>
+      <c r="FV2" s="1"/>
+      <c r="FW2" s="1"/>
+      <c r="FX2" s="1"/>
+      <c r="FY2" s="1"/>
+      <c r="FZ2" s="1"/>
+      <c r="GA2" s="1"/>
+      <c r="GB2" s="1"/>
+      <c r="GC2" s="1"/>
+      <c r="GD2" s="1"/>
+      <c r="GE2" s="1"/>
+      <c r="GF2" s="1"/>
+      <c r="GG2" s="1"/>
+      <c r="GH2" s="1"/>
+      <c r="GI2" s="1"/>
+      <c r="GJ2" s="1"/>
+      <c r="GK2" s="1"/>
+      <c r="GL2" s="1"/>
+      <c r="GM2" s="1"/>
+      <c r="GN2" s="1"/>
+      <c r="GO2" s="1"/>
+      <c r="GP2" s="1"/>
+      <c r="GQ2" s="1"/>
+      <c r="GR2" s="1"/>
+      <c r="GS2" s="1"/>
+      <c r="GT2" s="1"/>
+      <c r="GU2" s="1"/>
+    </row>
+    <row r="3" ht="20.1" customHeight="1" spans="1:4">
+      <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>5</v>
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="4" spans="3:5" ht="20.100000000000001" customHeight="1">
-      <c r="C4" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="3:5" ht="20.100000000000001" customHeight="1">
-      <c r="C5" s="7" t="s">
+    <row r="4" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B4" s="6">
         <v>1</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>0</v>
+      <c r="C4" s="6" t="s">
+        <v>10</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="3:5" ht="20.100000000000001" customHeight="1">
-      <c r="C6" s="4">
-        <v>1</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="4">
+      <c r="D4" s="6">
         <v>601700011</v>
       </c>
     </row>
-    <row r="7" spans="3:5" ht="20.100000000000001" customHeight="1">
-      <c r="C7" s="4">
+    <row r="5" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B5" s="6">
         <v>2</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>10</v>
+      <c r="C5" s="6" t="s">
+        <v>11</v>
       </c>
-      <c r="E7" s="4">
+      <c r="D5" s="6">
         <v>601700021</v>
       </c>
     </row>
-    <row r="8" spans="3:5" ht="20.100000000000001" customHeight="1">
-      <c r="C8" s="4">
+    <row r="6" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B6" s="6">
         <v>3</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>11</v>
+      <c r="C6" s="6" t="s">
+        <v>12</v>
       </c>
-      <c r="E8" s="4">
+      <c r="D6" s="6">
         <v>601700031</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
